--- a/04_Excel/Dashboard_Notes.xlsx
+++ b/04_Excel/Dashboard_Notes.xlsx
@@ -448,7 +448,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-12 06:48 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-13 07:06 UTC</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-12 06:48 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-13 07:06 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-12 06:48 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-13 07:06 UTC</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-12 06:48 UTC</t>
+          <t>2026-09-13 07:06 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/Dashboard_Notes.xlsx
+++ b/04_Excel/Dashboard_Notes.xlsx
@@ -448,7 +448,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-13 07:06 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-14 07:29 UTC</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-13 07:06 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-14 07:29 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-13 07:06 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-14 07:29 UTC</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-13 07:06 UTC</t>
+          <t>2026-09-14 07:29 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/Dashboard_Notes.xlsx
+++ b/04_Excel/Dashboard_Notes.xlsx
@@ -448,7 +448,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-14 07:29 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-15 07:07 UTC</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-14 07:29 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-15 07:07 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-14 07:29 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-15 07:07 UTC</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-14 07:29 UTC</t>
+          <t>2026-09-15 07:07 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/Dashboard_Notes.xlsx
+++ b/04_Excel/Dashboard_Notes.xlsx
@@ -448,7 +448,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-15 07:07 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-16 07:07 UTC</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-15 07:07 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-16 07:07 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-15 07:07 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-16 07:07 UTC</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-15 07:07 UTC</t>
+          <t>2026-09-16 07:07 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/Dashboard_Notes.xlsx
+++ b/04_Excel/Dashboard_Notes.xlsx
@@ -448,7 +448,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-16 07:07 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-17 07:06 UTC</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-16 07:07 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-17 07:06 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-16 07:07 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-17 07:06 UTC</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-16 07:07 UTC</t>
+          <t>2026-09-17 07:06 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/Dashboard_Notes.xlsx
+++ b/04_Excel/Dashboard_Notes.xlsx
@@ -448,7 +448,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-17 07:06 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-18 06:59 UTC</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-17 07:06 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-18 06:59 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-17 07:06 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-18 06:59 UTC</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-17 07:06 UTC</t>
+          <t>2026-09-18 06:59 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/Dashboard_Notes.xlsx
+++ b/04_Excel/Dashboard_Notes.xlsx
@@ -448,7 +448,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-18 06:59 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-19 06:57 UTC</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-18 06:59 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-19 06:57 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-18 06:59 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-19 06:57 UTC</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-18 06:59 UTC</t>
+          <t>2026-09-19 06:57 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/Dashboard_Notes.xlsx
+++ b/04_Excel/Dashboard_Notes.xlsx
@@ -448,7 +448,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-19 06:57 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-20 07:23 UTC</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-19 06:57 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-20 07:23 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-19 06:57 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-20 07:23 UTC</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-19 06:57 UTC</t>
+          <t>2026-09-20 07:23 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/Dashboard_Notes.xlsx
+++ b/04_Excel/Dashboard_Notes.xlsx
@@ -448,7 +448,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-20 07:23 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-21 07:33 UTC</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-20 07:23 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-21 07:33 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-20 07:23 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-21 07:33 UTC</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-20 07:23 UTC</t>
+          <t>2026-09-21 07:33 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/Dashboard_Notes.xlsx
+++ b/04_Excel/Dashboard_Notes.xlsx
@@ -448,7 +448,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-21 07:33 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-22 07:13 UTC</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-21 07:33 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-22 07:13 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-21 07:33 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-22 07:13 UTC</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-21 07:33 UTC</t>
+          <t>2026-09-22 07:13 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/Dashboard_Notes.xlsx
+++ b/04_Excel/Dashboard_Notes.xlsx
@@ -448,7 +448,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-22 07:13 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-23 07:14 UTC</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-22 07:13 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-23 07:14 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-22 07:13 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-23 07:14 UTC</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-22 07:13 UTC</t>
+          <t>2026-09-23 07:14 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/Dashboard_Notes.xlsx
+++ b/04_Excel/Dashboard_Notes.xlsx
@@ -448,7 +448,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-23 07:14 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-24 07:05 UTC</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-23 07:14 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-24 07:05 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-23 07:14 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-24 07:05 UTC</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-23 07:14 UTC</t>
+          <t>2026-09-24 07:05 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/Dashboard_Notes.xlsx
+++ b/04_Excel/Dashboard_Notes.xlsx
@@ -448,7 +448,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-24 07:05 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-25 07:03 UTC</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-24 07:05 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-25 07:03 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-24 07:05 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-25 07:03 UTC</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-24 07:05 UTC</t>
+          <t>2026-09-25 07:03 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/Dashboard_Notes.xlsx
+++ b/04_Excel/Dashboard_Notes.xlsx
@@ -448,7 +448,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-25 07:03 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-26 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-25 07:03 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-26 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-25 07:03 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-26 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-25 07:03 UTC</t>
+          <t>2026-09-26 07:00 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/Dashboard_Notes.xlsx
+++ b/04_Excel/Dashboard_Notes.xlsx
@@ -448,7 +448,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-26 07:00 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-27 07:31 UTC</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-26 07:00 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-27 07:31 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-26 07:00 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-27 07:31 UTC</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-26 07:00 UTC</t>
+          <t>2026-09-27 07:31 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/Dashboard_Notes.xlsx
+++ b/04_Excel/Dashboard_Notes.xlsx
@@ -448,7 +448,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-27 07:31 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-28 08:08 UTC</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-27 07:31 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-28 08:08 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-27 07:31 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-28 08:08 UTC</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-27 07:31 UTC</t>
+          <t>2026-09-28 08:08 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/Dashboard_Notes.xlsx
+++ b/04_Excel/Dashboard_Notes.xlsx
@@ -448,7 +448,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-28 08:08 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-29 07:49 UTC</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-28 08:08 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-29 07:49 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-28 08:08 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-29 07:49 UTC</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-28 08:08 UTC</t>
+          <t>2026-09-29 07:49 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/Dashboard_Notes.xlsx
+++ b/04_Excel/Dashboard_Notes.xlsx
@@ -448,7 +448,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-29 07:49 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-30 07:52 UTC</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-29 07:49 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-30 07:52 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-29 07:49 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-30 07:52 UTC</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29 07:49 UTC</t>
+          <t>2026-09-30 07:52 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/Dashboard_Notes.xlsx
+++ b/04_Excel/Dashboard_Notes.xlsx
@@ -448,7 +448,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-30 07:52 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-01 08:14 UTC</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-30 07:52 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-01 08:14 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-30 07:52 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-01 08:14 UTC</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-30 07:52 UTC</t>
+          <t>2026-10-01 08:14 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/Dashboard_Notes.xlsx
+++ b/04_Excel/Dashboard_Notes.xlsx
@@ -448,7 +448,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-01 08:14 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-01 12:32 UTC</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-01 08:14 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-01 12:32 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-01 08:14 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-01 12:32 UTC</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-01 08:14 UTC</t>
+          <t>2026-10-01 12:32 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/Dashboard_Notes.xlsx
+++ b/04_Excel/Dashboard_Notes.xlsx
@@ -448,7 +448,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-01 12:32 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-02 07:52 UTC</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-01 12:32 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-02 07:52 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-01 12:32 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-02 07:52 UTC</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-01 12:32 UTC</t>
+          <t>2026-10-02 07:52 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/Dashboard_Notes.xlsx
+++ b/04_Excel/Dashboard_Notes.xlsx
@@ -448,7 +448,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-02 07:52 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-03 07:31 UTC</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-02 07:52 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-03 07:31 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-02 07:52 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-03 07:31 UTC</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-02 07:52 UTC</t>
+          <t>2026-10-03 07:31 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/Dashboard_Notes.xlsx
+++ b/04_Excel/Dashboard_Notes.xlsx
@@ -448,7 +448,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-03 07:31 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-04 07:42 UTC</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-03 07:31 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-04 07:42 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-03 07:31 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-04 07:42 UTC</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-03 07:31 UTC</t>
+          <t>2026-10-04 07:42 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/Dashboard_Notes.xlsx
+++ b/04_Excel/Dashboard_Notes.xlsx
@@ -448,7 +448,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-04 07:42 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-05 08:12 UTC</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-04 07:42 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-05 08:12 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-04 07:42 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-05 08:12 UTC</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-04 07:42 UTC</t>
+          <t>2026-10-05 08:12 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/Dashboard_Notes.xlsx
+++ b/04_Excel/Dashboard_Notes.xlsx
@@ -448,7 +448,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-05 08:12 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-06 08:29 UTC</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-05 08:12 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-06 08:29 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-05 08:12 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-06 08:29 UTC</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-05 08:12 UTC</t>
+          <t>2026-10-06 08:29 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/Dashboard_Notes.xlsx
+++ b/04_Excel/Dashboard_Notes.xlsx
@@ -448,7 +448,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-06 08:29 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-07 08:05 UTC</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-06 08:29 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-07 08:05 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-06 08:29 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-07 08:05 UTC</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 08:29 UTC</t>
+          <t>2026-10-07 08:05 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/Dashboard_Notes.xlsx
+++ b/04_Excel/Dashboard_Notes.xlsx
@@ -448,7 +448,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-07 08:05 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-08 08:21 UTC</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-07 08:05 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-08 08:21 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-07 08:05 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-08 08:21 UTC</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-07 08:05 UTC</t>
+          <t>2026-10-08 08:21 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/Dashboard_Notes.xlsx
+++ b/04_Excel/Dashboard_Notes.xlsx
@@ -448,7 +448,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-08 08:21 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-09 08:24 UTC</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-08 08:21 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-09 08:24 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-08 08:21 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-09 08:24 UTC</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-08 08:21 UTC</t>
+          <t>2026-10-09 08:24 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/Dashboard_Notes.xlsx
+++ b/04_Excel/Dashboard_Notes.xlsx
@@ -448,7 +448,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-09 08:24 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-10 08:01 UTC</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-09 08:24 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-10 08:01 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-09 08:24 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-10 08:01 UTC</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-09 08:24 UTC</t>
+          <t>2026-10-10 08:01 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/Dashboard_Notes.xlsx
+++ b/04_Excel/Dashboard_Notes.xlsx
@@ -448,7 +448,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-10 08:01 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-11 08:13 UTC</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-10 08:01 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-11 08:13 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-10 08:01 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-11 08:13 UTC</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-10 08:01 UTC</t>
+          <t>2026-10-11 08:13 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/Dashboard_Notes.xlsx
+++ b/04_Excel/Dashboard_Notes.xlsx
@@ -448,7 +448,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-11 08:13 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-12 08:30 UTC</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-11 08:13 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-12 08:30 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-11 08:13 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-12 08:30 UTC</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-11 08:13 UTC</t>
+          <t>2026-10-12 08:30 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/Dashboard_Notes.xlsx
+++ b/04_Excel/Dashboard_Notes.xlsx
@@ -448,7 +448,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-12 08:30 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-13 08:52 UTC</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-12 08:30 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-13 08:52 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-12 08:30 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-13 08:52 UTC</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-12 08:30 UTC</t>
+          <t>2026-10-13 08:52 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/Dashboard_Notes.xlsx
+++ b/04_Excel/Dashboard_Notes.xlsx
@@ -448,7 +448,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-13 08:52 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-14 07:02 UTC</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-13 08:52 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-14 07:02 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-13 08:52 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-14 07:02 UTC</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-13 08:52 UTC</t>
+          <t>2026-10-14 07:02 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/Dashboard_Notes.xlsx
+++ b/04_Excel/Dashboard_Notes.xlsx
@@ -448,7 +448,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-14 07:02 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-15 06:53 UTC</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-14 07:02 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-15 06:53 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-14 07:02 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-15 06:53 UTC</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 07:02 UTC</t>
+          <t>2026-10-15 06:53 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/Dashboard_Notes.xlsx
+++ b/04_Excel/Dashboard_Notes.xlsx
@@ -448,7 +448,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-15 06:53 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-16 06:40 UTC</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-15 06:53 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-16 06:40 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-15 06:53 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-16 06:40 UTC</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-15 06:53 UTC</t>
+          <t>2026-10-16 06:40 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/Dashboard_Notes.xlsx
+++ b/04_Excel/Dashboard_Notes.xlsx
@@ -448,7 +448,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-16 06:40 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-17 06:29 UTC</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-16 06:40 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-17 06:29 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-16 06:40 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-17 06:29 UTC</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-16 06:40 UTC</t>
+          <t>2026-10-17 06:29 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/Dashboard_Notes.xlsx
+++ b/04_Excel/Dashboard_Notes.xlsx
@@ -448,7 +448,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-17 06:29 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-18 06:54 UTC</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-17 06:29 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-18 06:54 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-17 06:29 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-18 06:54 UTC</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-17 06:29 UTC</t>
+          <t>2026-10-18 06:54 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/Dashboard_Notes.xlsx
+++ b/04_Excel/Dashboard_Notes.xlsx
@@ -448,7 +448,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-18 06:54 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-19 07:14 UTC</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-18 06:54 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-19 07:14 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-18 06:54 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-19 07:14 UTC</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-18 06:54 UTC</t>
+          <t>2026-10-19 07:14 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/Dashboard_Notes.xlsx
+++ b/04_Excel/Dashboard_Notes.xlsx
@@ -448,7 +448,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-19 07:14 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-20 07:04 UTC</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-19 07:14 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-20 07:04 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-19 07:14 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-20 07:04 UTC</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-19 07:14 UTC</t>
+          <t>2026-10-20 07:04 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/Dashboard_Notes.xlsx
+++ b/04_Excel/Dashboard_Notes.xlsx
@@ -448,7 +448,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-20 07:04 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-21 06:57 UTC</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-20 07:04 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-21 06:57 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-20 07:04 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-21 06:57 UTC</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-20 07:04 UTC</t>
+          <t>2026-10-21 06:57 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/Dashboard_Notes.xlsx
+++ b/04_Excel/Dashboard_Notes.xlsx
@@ -448,7 +448,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-21 06:57 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-22 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-21 06:57 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-22 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-21 06:57 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-22 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-21 06:57 UTC</t>
+          <t>2026-10-22 07:00 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/Dashboard_Notes.xlsx
+++ b/04_Excel/Dashboard_Notes.xlsx
@@ -448,7 +448,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-22 07:00 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-23 06:53 UTC</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-22 07:00 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-23 06:53 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-22 07:00 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-23 06:53 UTC</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-22 07:00 UTC</t>
+          <t>2026-10-23 06:53 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/Dashboard_Notes.xlsx
+++ b/04_Excel/Dashboard_Notes.xlsx
@@ -448,7 +448,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-23 06:53 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-24 06:49 UTC</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-23 06:53 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-24 06:49 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-23 06:53 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-24 06:49 UTC</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-23 06:53 UTC</t>
+          <t>2026-10-24 06:49 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/Dashboard_Notes.xlsx
+++ b/04_Excel/Dashboard_Notes.xlsx
@@ -448,7 +448,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-24 06:49 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-25 07:13 UTC</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-24 06:49 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-25 07:13 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-24 06:49 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-25 07:13 UTC</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-24 06:49 UTC</t>
+          <t>2026-10-25 07:13 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/Dashboard_Notes.xlsx
+++ b/04_Excel/Dashboard_Notes.xlsx
@@ -448,7 +448,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-25 07:13 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-26 07:21 UTC</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-25 07:13 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-26 07:21 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-25 07:13 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-26 07:21 UTC</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-25 07:13 UTC</t>
+          <t>2026-10-26 07:21 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/Dashboard_Notes.xlsx
+++ b/04_Excel/Dashboard_Notes.xlsx
@@ -448,7 +448,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-26 07:21 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-27 07:13 UTC</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-26 07:21 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-27 07:13 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-26 07:21 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-27 07:13 UTC</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-26 07:21 UTC</t>
+          <t>2026-10-27 07:13 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/Dashboard_Notes.xlsx
+++ b/04_Excel/Dashboard_Notes.xlsx
@@ -448,7 +448,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-27 07:13 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-28 07:51 UTC</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-27 07:13 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-28 07:51 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-27 07:13 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-28 07:51 UTC</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-27 07:13 UTC</t>
+          <t>2026-10-28 07:51 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/Dashboard_Notes.xlsx
+++ b/04_Excel/Dashboard_Notes.xlsx
@@ -448,7 +448,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-28 07:51 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-29 07:57 UTC</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-28 07:51 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-29 07:57 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-28 07:51 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-29 07:57 UTC</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-28 07:51 UTC</t>
+          <t>2026-10-29 07:57 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/Dashboard_Notes.xlsx
+++ b/04_Excel/Dashboard_Notes.xlsx
@@ -448,7 +448,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-29 07:57 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-30 07:59 UTC</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-29 07:57 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-30 07:59 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-29 07:57 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-30 07:59 UTC</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-29 07:57 UTC</t>
+          <t>2026-10-30 07:59 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/Dashboard_Notes.xlsx
+++ b/04_Excel/Dashboard_Notes.xlsx
@@ -448,7 +448,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-30 07:59 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-31 07:56 UTC</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-30 07:59 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-31 07:56 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-30 07:59 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-31 07:56 UTC</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-30 07:59 UTC</t>
+          <t>2026-10-31 07:56 UTC</t>
         </is>
       </c>
     </row>
